--- a/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-raw-mvtec_screw_medium.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-raw-mvtec_screw_medium.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="padim" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stfpm" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="uflow" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,105 +478,95 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>export:test/iter_time</t>
+          <t>torch:test/latency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/iter_time</t>
+          <t>export:test/latency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/latency</t>
+          <t>optimize:test/latency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>export:test/latency</t>
+          <t>torch:test/e2e_time</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/latency</t>
+          <t>export:test/e2e_time</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/e2e_time</t>
+          <t>optimize:test/e2e_time</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>export:test/e2e_time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/e2e_time</t>
+          <t>task</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>data_group</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>data_group</t>
+          <t>otx_version</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>otx_ref</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otx_version</t>
+          <t>test_branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otx_ref</t>
+          <t>test_commit</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>test_branch</t>
+          <t>cpu_info</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>test_commit</t>
+          <t>accelerator_info</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>cpu_info</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>accelerator_info</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>machine_name</t>
         </is>
@@ -589,116 +580,107 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>20.36874532699585</v>
+        <v>22.87647986412048</v>
       </c>
       <c r="D2" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1123277321457862</v>
+        <v>0.1793553978204727</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8799999952316284</v>
+        <v>0.8880000114440918</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8550724387168884</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3484512865543365</v>
+        <v>0.2473030984401703</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0712776333093643</v>
+        <v>0.0130292897423108</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0582982935011386</v>
+        <v>0.0555113936463991</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0157068704565366</v>
+        <v>0.0435973117748896</v>
       </c>
       <c r="M2" t="n">
-        <v>0.079462860027949</v>
+        <v>6.254059076309204</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0662238627672195</v>
+        <v>26.64546895027161</v>
       </c>
       <c r="O2" t="n">
-        <v>7.539297819137573</v>
-      </c>
-      <c r="P2" t="n">
-        <v>38.14217281341553</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>31.78745412826538</v>
+        <v>20.92670965194702</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250714-163702</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250529-155840</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_screw_medium</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>mvtec_screw_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -710,116 +692,107 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>20.50026893615723</v>
+        <v>21.89305758476257</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9300000071525574</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1177099868655204</v>
+        <v>0.1763277649879455</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8613138794898987</v>
+        <v>0.8650793433189392</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8530465960502625</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3494672179222107</v>
+        <v>0.1832786500453949</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07064174115657799</v>
+        <v>0.009929218888282699</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0585057437419891</v>
+        <v>0.0562822346885999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0157973100741704</v>
+        <v>0.0431917935609817</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0788489441076914</v>
+        <v>4.766025066375732</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0663375621040662</v>
+        <v>27.01547265052796</v>
       </c>
       <c r="O3" t="n">
-        <v>7.582708835601807</v>
-      </c>
-      <c r="P3" t="n">
-        <v>37.84749317169189</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>31.84202980995178</v>
+        <v>20.73206090927124</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250714-163935</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250529-160102</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_screw_medium</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>mvtec_screw_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -831,116 +804,107 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>20.53516840934753</v>
+        <v>21.02128529548645</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9300000071525574</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1077926754951477</v>
+        <v>0.1731191277503967</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8837209343910217</v>
+        <v>0.8838951587677002</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8561151027679443</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8561151027679443</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3503972887992859</v>
+        <v>0.2178758680820465</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0706370621919632</v>
+        <v>0.0116540054480234</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0584580190479755</v>
+        <v>0.0550779854257901</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0153760184844334</v>
+        <v>0.0430213615298271</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0782794257005055</v>
+        <v>5.59392261505127</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0656157791614532</v>
+        <v>26.43743300437927</v>
       </c>
       <c r="O4" t="n">
-        <v>7.380488872528076</v>
-      </c>
-      <c r="P4" t="n">
-        <v>37.57412433624268</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>31.49557399749756</v>
+        <v>20.65025353431702</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250714-164205</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250529-160321</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_screw_medium</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>mvtec_screw_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -952,116 +916,107 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>20.50972318649292</v>
+        <v>20.87186479568481</v>
       </c>
       <c r="D5" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1104771867394447</v>
+        <v>0.1715736240148544</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8571428656578064</v>
+        <v>0.8780487775802612</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8530465960502625</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3542719483375549</v>
+        <v>0.1887030601501464</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06978019326925269</v>
+        <v>0.0100847134987513</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0584462992846965</v>
+        <v>0.0558824876944224</v>
       </c>
       <c r="L5" t="n">
-        <v>0.016064415872097</v>
+        <v>0.0430457234382629</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0775095244248708</v>
+        <v>4.840662479400635</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0660251249869664</v>
+        <v>26.82359409332276</v>
       </c>
       <c r="O5" t="n">
-        <v>7.710919618606567</v>
-      </c>
-      <c r="P5" t="n">
-        <v>37.20457172393799</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>31.6920599937439</v>
+        <v>20.66194725036621</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250714-164434</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250529-160540</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_screw_medium</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>mvtec_screw_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1073,116 +1028,107 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>20.5469343662262</v>
+        <v>20.44818782806396</v>
       </c>
       <c r="D6" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1087374463677406</v>
+        <v>0.1723885536193847</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8764940500259399</v>
+        <v>0.8730158805847168</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8529411554336548</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8405796885490417</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3515272736549377</v>
+        <v>0.2230813056230545</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07087402045726771</v>
+        <v>0.0115383356809616</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0581930950284004</v>
+        <v>0.0544393867254257</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0155014057954152</v>
+        <v>0.0426415160298347</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0783500070373217</v>
+        <v>5.538401126861572</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06573647360006959</v>
+        <v>26.13090562820435</v>
       </c>
       <c r="O6" t="n">
-        <v>7.440674781799316</v>
-      </c>
-      <c r="P6" t="n">
-        <v>37.60800337791443</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>31.55350732803345</v>
+        <v>20.46792769432068</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250714-164703</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250529-160800</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_screw_medium</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>mvtec_screw_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,105 +1194,95 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>export:test/iter_time</t>
+          <t>torch:test/latency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/iter_time</t>
+          <t>export:test/latency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/latency</t>
+          <t>optimize:test/latency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>export:test/latency</t>
+          <t>torch:test/e2e_time</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/latency</t>
+          <t>export:test/e2e_time</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/e2e_time</t>
+          <t>optimize:test/e2e_time</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>export:test/e2e_time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/e2e_time</t>
+          <t>task</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>data_group</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>data_group</t>
+          <t>otx_version</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>otx_ref</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otx_version</t>
+          <t>test_branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otx_ref</t>
+          <t>test_commit</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>test_branch</t>
+          <t>cpu_info</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>test_commit</t>
+          <t>accelerator_info</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>cpu_info</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>accelerator_info</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>machine_name</t>
         </is>
@@ -1357,119 +1293,110 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>69.06945705413818</v>
+        <v>176.0425872802734</v>
       </c>
       <c r="D2" t="n">
-        <v>1.759999990463257</v>
+        <v>1.639999985694885</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0984962403774261</v>
+        <v>0.1717104216416676</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8489208817481995</v>
+        <v>0.8666666746139526</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8530465960502625</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8530465960502625</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1916875094175338</v>
+        <v>0.1778694093227386</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0642069801688194</v>
+        <v>0.009674725929896001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0527924969792366</v>
+        <v>0.0463100776076316</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0110498026013374</v>
+        <v>0.0336526562770207</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07173657566308971</v>
+        <v>4.643868446350098</v>
       </c>
       <c r="N2" t="n">
-        <v>0.060870553056399</v>
+        <v>22.22883725166321</v>
       </c>
       <c r="O2" t="n">
-        <v>5.303905248641968</v>
-      </c>
-      <c r="P2" t="n">
-        <v>34.43355631828308</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>29.21786546707153</v>
+        <v>16.15327501296997</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250716-002909</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250529-172144</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_screw_medium</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>mvtec_screw_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1478,119 +1405,110 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>68.18561673164368</v>
+        <v>163.0548710823059</v>
       </c>
       <c r="D3" t="n">
-        <v>1.789999961853027</v>
+        <v>1.620000004768372</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0991669014096259</v>
+        <v>0.1728149273178794</v>
       </c>
       <c r="F3" t="n">
         <v>0.8489208817481995</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8530465960502625</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8530465960502625</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1889301985502243</v>
+        <v>0.1833141595125198</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0634510368108749</v>
+        <v>0.0100401356816291</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0523563027381897</v>
+        <v>0.0464491640528043</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0104179585973421</v>
+        <v>0.0340749661127726</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0712430213888486</v>
+        <v>4.819265127182007</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0603981683651606</v>
+        <v>22.29559874534607</v>
       </c>
       <c r="O3" t="n">
-        <v>5.000620126724243</v>
-      </c>
-      <c r="P3" t="n">
-        <v>34.19665026664734</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>28.9911208152771</v>
+        <v>16.35598373413086</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250716-003402</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250529-172445</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_screw_medium</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>mvtec_screw_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1599,119 +1517,110 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>68.39424729347229</v>
+        <v>121.9924175739288</v>
       </c>
       <c r="D4" t="n">
-        <v>1.759999990463257</v>
+        <v>1.590000033378601</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0995299458503722</v>
+        <v>0.1729783825576304</v>
       </c>
       <c r="F4" t="n">
         <v>0.8489208817481995</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8530465960502625</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8530465960502625</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1793362349271774</v>
+        <v>0.1804342418909073</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0634206607937812</v>
+        <v>0.009694629907608001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0533965937793254</v>
+        <v>0.0466747686266899</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0101872767011324</v>
+        <v>0.0343541497985522</v>
       </c>
       <c r="M4" t="n">
-        <v>0.070791674653689</v>
+        <v>4.653422355651856</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0614684085051218</v>
+        <v>22.40388894081116</v>
       </c>
       <c r="O4" t="n">
-        <v>4.889892816543579</v>
-      </c>
-      <c r="P4" t="n">
-        <v>33.98000383377075</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>29.5048360824585</v>
+        <v>16.48999190330505</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250716-003844</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250529-172743</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_screw_medium</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>mvtec_screw_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1720,119 +1629,110 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>67.95982718467712</v>
+        <v>176.2922024726868</v>
       </c>
       <c r="D5" t="n">
-        <v>1.730000019073486</v>
+        <v>1.590000033378601</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09899368584156019</v>
+        <v>0.173967320472002</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8489208817481995</v>
+        <v>0.8957529067993164</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8530465960502625</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8530465960502625</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1659266650676727</v>
+        <v>0.1751763969659805</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0647410303354263</v>
+        <v>0.0097179189324378</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0532989166676998</v>
+        <v>0.0471709132194519</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0097895274559656</v>
+        <v>0.034298917154471</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07227972745895379</v>
+        <v>4.66460108757019</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0613587056597073</v>
+        <v>22.64203834533692</v>
       </c>
       <c r="O5" t="n">
-        <v>4.698973178863525</v>
-      </c>
-      <c r="P5" t="n">
-        <v>34.69426918029785</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>29.45217871665954</v>
+        <v>16.46348023414612</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250716-004244</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250529-173040</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_screw_medium</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>mvtec_screw_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1841,119 +1741,826 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>68.00501418113708</v>
+        <v>135.4267737865448</v>
       </c>
       <c r="D6" t="n">
-        <v>1.759999990463257</v>
+        <v>1.559999942779541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0984095662832259</v>
+        <v>0.1726463023159239</v>
       </c>
       <c r="F6" t="n">
         <v>0.8489208817481995</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8530465960502625</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8530465960502625</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1813794523477554</v>
+        <v>0.1798025667667389</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0631697624921798</v>
+        <v>0.0099744856357574</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0529030673205852</v>
+        <v>0.046549638112386</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0105555107196172</v>
+        <v>0.0337029362718264</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0705116614699363</v>
+        <v>4.787753105163574</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0608097011844317</v>
+        <v>22.34382629394531</v>
       </c>
       <c r="O6" t="n">
-        <v>5.06664514541626</v>
-      </c>
-      <c r="P6" t="n">
-        <v>33.84559750556946</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>29.18865656852722</v>
+        <v>16.17740941047668</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250716-004739</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250529-173338</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>mvtec_screw_medium</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>training:epoch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>training:e2e_time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>training:gpu_mem</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>training:train/iter_time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/iter_time</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/latency</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/latency</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/latency</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>data_group</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>otx_version</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>otx_ref</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>test_branch</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>test_commit</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>cpu_info</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>accelerator_info</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>user_name</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>machine_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>199</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2852.644351005554</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2031430110110709</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8550724387168884</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3219891786575317</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.016334160665671</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0762951304515202</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0676643465956052</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7.840397119522095</v>
+      </c>
+      <c r="N2" t="n">
+        <v>36.62166261672974</v>
+      </c>
+      <c r="O2" t="n">
+        <v>32.4788863658905</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250714-221336</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>mvtec_screw_medium</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>199</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2840.012531042099</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.159999847412109</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2028923522138116</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8509091138839722</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3093318343162536</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0150615324576695</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0758697539567947</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.06847308923800779</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7.229535579681396</v>
+      </c>
+      <c r="N3" t="n">
+        <v>36.41748189926148</v>
+      </c>
+      <c r="O3" t="n">
+        <v>32.86708283424377</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250714-230345</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>mvtec_screw_medium</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>199</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2854.696831226349</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.079999923706055</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2031015487172495</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8613138794898987</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2696432173252105</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0131830508510271</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.07737858345111211</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.06847949922084801</v>
+      </c>
+      <c r="M4" t="n">
+        <v>6.327864408493042</v>
+      </c>
+      <c r="N4" t="n">
+        <v>37.14172005653381</v>
+      </c>
+      <c r="O4" t="n">
+        <v>32.87015962600708</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250714-235341</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>mvtec_screw_medium</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>199</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2821.255435943604</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5.940000057220459</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2003950127704658</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8550186157226562</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3614486753940582</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0164536197980244</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0780545155207316</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.06861640761295951</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7.897737503051758</v>
+      </c>
+      <c r="N5" t="n">
+        <v>37.46616744995117</v>
+      </c>
+      <c r="O5" t="n">
+        <v>32.93587565422058</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250715-004331</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>mvtec_screw_medium</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>199</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2800.275090694427</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.289999961853027</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2019477053802816</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8689138293266296</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3094400465488434</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0153441255291303</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.07798921863238011</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0681196972727775</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7.365180253982544</v>
+      </c>
+      <c r="N6" t="n">
+        <v>37.43482494354248</v>
+      </c>
+      <c r="O6" t="n">
+        <v>32.69745469093323</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250715-013250</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_screw_medium</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>mvtec_screw_medium</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
